--- a/architectures and decision enablers/architecture decision enabler/swift-threat-assessment/Swift_Security_Assessment.xlsx
+++ b/architectures and decision enablers/architecture decision enabler/swift-threat-assessment/Swift_Security_Assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amitp\Documents\portfolio-repo\architectures and decision enablers\architecture decision enabler\swift-threat-assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D3AE29-E2DA-4A71-B334-B52F04ED0AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3E5668-613B-477D-93B3-37357F5C09A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D62D5DFD-F87A-4D1C-B4C2-9718B4BFE1A3}"/>
   </bookViews>
   <sheets>
     <sheet name="User_Responses" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1844,14 +1844,10 @@
     <t xml:space="preserve">Widespread failure or complete absence of standard security baselines. Credential hygiene is absent, access groups are unmonitored, and third-party interactions introduce severe risk </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
+    <t>Catastrophic exposure. The organization is exceptionally vulnerable to imminent fraud, ransomware distribution, or extensive long-term data exfiltration</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">☠️ State 4: Critical Threat Posture (Score: 75.01% – 100%)
 </t>
     </r>
@@ -1867,9 +1863,6 @@
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>Catastrophic exposure. The organization is exceptionally vulnerable to imminent fraud, ransomware distribution, or extensive long-term data exfiltration</t>
   </si>
 </sst>
 </file>
@@ -2072,34 +2065,6 @@
   </cellStyles>
   <dxfs count="11">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color theme="8"/>
-        </left>
-        <right style="thin">
-          <color theme="8"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -2107,16 +2072,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="medium">
+        <top style="thin">
           <color theme="8"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="medium">
           <color theme="8"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -2130,13 +2095,22 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="16"/>
+        <sz val="14"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="8"/>
+        </left>
+        <right style="thin">
+          <color theme="8"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -2187,6 +2161,25 @@
           <color rgb="FFDCDFE5"/>
         </bottom>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3556,7 +3549,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56BEEA62-38BE-4FD4-B8B0-854F4BE485B1}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56BEEA62-38BE-4FD4-B8B0-854F4BE485B1}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="B25:D41" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0" sortType="descending">
@@ -3693,13 +3686,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCC7E8A2-E37F-41A7-86BC-F8FA97E525B8}" name="Table1" displayName="Table1" ref="A1:D78" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCC7E8A2-E37F-41A7-86BC-F8FA97E525B8}" name="Table1" displayName="Table1" ref="A1:D78" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9">
   <autoFilter ref="A1:D78" xr:uid="{BCC7E8A2-E37F-41A7-86BC-F8FA97E525B8}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{67AED665-9562-40D2-B38F-062B6736059F}" name="Category" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{03F2FCFE-1DC5-4C77-B920-EF0B3618A66A}" name="Client-Specific Question" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{52A3C89F-0892-4359-836A-E4C61F7FF7C1}" name="User Priority" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{49C6DBFA-626B-4C33-9B5E-2F7D83EB221F}" name="User Score" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{67AED665-9562-40D2-B38F-062B6736059F}" name="Category" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{03F2FCFE-1DC5-4C77-B920-EF0B3618A66A}" name="Client-Specific Question" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{52A3C89F-0892-4359-836A-E4C61F7FF7C1}" name="User Priority" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{49C6DBFA-626B-4C33-9B5E-2F7D83EB221F}" name="User Score" dataDxfId="5">
       <calculatedColumnFormula array="1">_xlfn.SWITCH(C2,"A", 0.25,"B", 0.5, "C", 0.75,"D", 1)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3721,12 +3714,12 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E2B15CCF-D726-40C5-8B85-899402E9AE03}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E2B15CCF-D726-40C5-8B85-899402E9AE03}" name="Table3" displayName="Table3" ref="A1:C5" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="A1:C5" xr:uid="{E2B15CCF-D726-40C5-8B85-899402E9AE03}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{957247C0-1F8E-4F1F-BBB9-AB5E4959E43C}" name="States"/>
-    <tableColumn id="2" xr3:uid="{09A551D2-0ADE-4765-8888-B42CA7137A32}" name="Definitions" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{487F9945-FAA7-488D-BFDC-38B5E2BCA065}" name="Operational Impact" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{09A551D2-0ADE-4765-8888-B42CA7137A32}" name="Definitions" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{487F9945-FAA7-488D-BFDC-38B5E2BCA065}" name="Operational Impact" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium24" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5768,13 +5761,13 @@
     </row>
     <row r="5" spans="1:4" ht="102" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>119</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D5" s="2"/>
     </row>
